--- a/4.1 Myrmidon Happy reef/output/yearly_benthic_cover_growth_param_0.5.xlsx
+++ b/4.1 Myrmidon Happy reef/output/yearly_benthic_cover_growth_param_0.5.xlsx
@@ -541,34 +541,34 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>81.02862391628865</v>
+        <v>80.98177313948561</v>
       </c>
       <c r="C3" t="n">
-        <v>73.66751280517752</v>
+        <v>73.6206620283745</v>
       </c>
       <c r="D3" t="n">
-        <v>1.000342931945801</v>
+        <v>1.000343130411954</v>
       </c>
       <c r="E3" t="n">
-        <v>1.868153234977613</v>
+        <v>1.821286752886324</v>
       </c>
       <c r="F3" t="n">
-        <v>8.402880628344727</v>
+        <v>8.402882295460415</v>
       </c>
       <c r="G3" t="n">
-        <v>62.42139895341797</v>
+        <v>62.42141133770593</v>
       </c>
       <c r="H3" t="n">
-        <v>5.501886125701905</v>
+        <v>5.501887217265748</v>
       </c>
       <c r="I3" t="n">
-        <v>0.833619109954834</v>
+        <v>0.8336192753432952</v>
       </c>
       <c r="J3" t="n">
-        <v>1.000342931945801</v>
+        <v>1.000343130411954</v>
       </c>
       <c r="K3" t="n">
-        <v>18.97137608371136</v>
+        <v>19.01822686051439</v>
       </c>
       <c r="L3" t="n">
         <v>7.333333333333333</v>
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>81.22992637259708</v>
+        <v>81.25472531960634</v>
       </c>
       <c r="C4" t="n">
-        <v>74.00985863693271</v>
+        <v>74.03465615149415</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9995854029447633</v>
+        <v>0.9993796030037663</v>
       </c>
       <c r="E4" t="n">
-        <v>2.251971272150684</v>
+        <v>2.289816196686135</v>
       </c>
       <c r="F4" t="n">
-        <v>8.405276707255995</v>
+        <v>8.405277643830393</v>
       </c>
       <c r="G4" t="n">
-        <v>62.37412914375323</v>
+        <v>62.36128722743501</v>
       </c>
       <c r="H4" t="n">
-        <v>5.503454986893806</v>
+        <v>5.503455600127043</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6948806801633594</v>
+        <v>0.6948807575917985</v>
       </c>
       <c r="J4" t="n">
-        <v>1.000628179435237</v>
+        <v>1.00062829093219</v>
       </c>
       <c r="K4" t="n">
-        <v>18.77007362740294</v>
+        <v>18.74527468039366</v>
       </c>
       <c r="L4" t="n">
-        <v>7.196911649276734</v>
+        <v>7.196913077130448</v>
       </c>
       <c r="M4" t="n">
-        <v>99.97684391361237</v>
+        <v>99.97684390901826</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>81.51156033651435</v>
+        <v>81.53403254146457</v>
       </c>
       <c r="C5" t="n">
-        <v>74.40910769560021</v>
+        <v>74.43157910914572</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9963850118795992</v>
+        <v>0.9959193570186317</v>
       </c>
       <c r="E5" t="n">
-        <v>2.848654890325579</v>
+        <v>2.900648898181288</v>
       </c>
       <c r="F5" t="n">
-        <v>8.407267579535629</v>
+        <v>8.407267967704492</v>
       </c>
       <c r="G5" t="n">
-        <v>62.174424741287</v>
+        <v>62.14536787796261</v>
       </c>
       <c r="H5" t="n">
-        <v>5.504758534219758</v>
+        <v>5.504758788377941</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5792043912268263</v>
+        <v>0.5792044179690595</v>
       </c>
       <c r="J5" t="n">
-        <v>1.000865188039956</v>
+        <v>1.000865234250535</v>
       </c>
       <c r="K5" t="n">
-        <v>18.48843966348565</v>
+        <v>18.46596745853545</v>
       </c>
       <c r="L5" t="n">
-        <v>7.08315039979851</v>
+        <v>7.083151189052398</v>
       </c>
       <c r="M5" t="n">
-        <v>99.98069775888438</v>
+        <v>99.98069775673356</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>81.1458789516365</v>
+        <v>81.25243784745543</v>
       </c>
       <c r="C6" t="n">
-        <v>74.141495892487</v>
+        <v>74.24805446490917</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9900856237669921</v>
+        <v>0.9891353195859999</v>
       </c>
       <c r="E6" t="n">
-        <v>2.975835652380662</v>
+        <v>3.14264712699789</v>
       </c>
       <c r="F6" t="n">
-        <v>8.408934841580203</v>
+        <v>8.408933042931052</v>
       </c>
       <c r="G6" t="n">
-        <v>61.78134292306031</v>
+        <v>61.72204394216639</v>
       </c>
       <c r="H6" t="n">
-        <v>5.5058501938918</v>
+        <v>5.505849016204856</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4827660453398394</v>
+        <v>0.482765942077446</v>
       </c>
       <c r="J6" t="n">
-        <v>1.001063671616691</v>
+        <v>1.001063457491792</v>
       </c>
       <c r="K6" t="n">
-        <v>18.8541210483635</v>
+        <v>18.74756215254456</v>
       </c>
       <c r="L6" t="n">
-        <v>6.98829404828207</v>
+        <v>6.988294370936026</v>
       </c>
       <c r="M6" t="n">
-        <v>99.98391098913257</v>
+        <v>99.98391098838977</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>80.79740760401407</v>
+        <v>80.91722991131741</v>
       </c>
       <c r="C7" t="n">
-        <v>73.87477853279628</v>
+        <v>73.99460232083183</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9794312462833882</v>
+        <v>0.9781866061672194</v>
       </c>
       <c r="E7" t="n">
-        <v>3.380770026636193</v>
+        <v>3.579509560935427</v>
       </c>
       <c r="F7" t="n">
-        <v>8.410330727298714</v>
+        <v>8.410326860681794</v>
       </c>
       <c r="G7" t="n">
-        <v>61.11650976808343</v>
+        <v>61.03884422483449</v>
       </c>
       <c r="H7" t="n">
-        <v>5.506764166683682</v>
+        <v>5.506761634970222</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4023718205407433</v>
+        <v>0.4023716355518599</v>
       </c>
       <c r="J7" t="n">
-        <v>1.001229848487942</v>
+        <v>1.001229388176404</v>
       </c>
       <c r="K7" t="n">
-        <v>19.20259239598591</v>
+        <v>19.08277008868259</v>
       </c>
       <c r="L7" t="n">
-        <v>6.909218903291691</v>
+        <v>6.909217425427853</v>
       </c>
       <c r="M7" t="n">
-        <v>99.98658983207389</v>
+        <v>99.98658983494228</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>79.89884338274811</v>
+        <v>80.05100445942934</v>
       </c>
       <c r="C8" t="n">
-        <v>73.04436252211084</v>
+        <v>73.19652675011304</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9632075822892453</v>
+        <v>0.9614605618553075</v>
       </c>
       <c r="E8" t="n">
-        <v>3.575713953550028</v>
+        <v>3.838647197604469</v>
       </c>
       <c r="F8" t="n">
-        <v>8.411507407365415</v>
+        <v>8.411501302720854</v>
       </c>
       <c r="G8" t="n">
-        <v>60.10415313484891</v>
+        <v>59.99513905977118</v>
       </c>
       <c r="H8" t="n">
-        <v>5.50753461196545</v>
+        <v>5.50753061487675</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3353567632808025</v>
+        <v>0.3353565198959083</v>
       </c>
       <c r="J8" t="n">
-        <v>1.001369929448264</v>
+        <v>1.001369202704864</v>
       </c>
       <c r="K8" t="n">
-        <v>20.10115661725189</v>
+        <v>19.94899554057068</v>
       </c>
       <c r="L8" t="n">
-        <v>6.843303865622245</v>
+        <v>6.843300719439842</v>
       </c>
       <c r="M8" t="n">
-        <v>99.98882300498498</v>
+        <v>99.98882301012355</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>78.32728129274392</v>
+        <v>78.54465005194119</v>
       </c>
       <c r="C9" t="n">
-        <v>71.52959731628283</v>
+        <v>71.74697100889365</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9399024632763632</v>
+        <v>0.937787834798256</v>
       </c>
       <c r="E9" t="n">
-        <v>3.535781266177664</v>
+        <v>3.887233508777706</v>
       </c>
       <c r="F9" t="n">
-        <v>8.412507907154483</v>
+        <v>8.412499031895385</v>
       </c>
       <c r="G9" t="n">
-        <v>58.64991370844506</v>
+        <v>58.51796089141116</v>
       </c>
       <c r="H9" t="n">
-        <v>5.508189701113055</v>
+        <v>5.508183889931503</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2794972100112866</v>
+        <v>0.2794969151396284</v>
       </c>
       <c r="J9" t="n">
-        <v>1.00148903656601</v>
+        <v>1.001487979987546</v>
       </c>
       <c r="K9" t="n">
-        <v>21.6727187072561</v>
+        <v>21.45534994805882</v>
       </c>
       <c r="L9" t="n">
-        <v>6.788368510814383</v>
+        <v>6.788363584161537</v>
       </c>
       <c r="M9" t="n">
-        <v>99.99068453435331</v>
+        <v>99.99068454111401</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>76.35865134375707</v>
+        <v>76.53322572052625</v>
       </c>
       <c r="C10" t="n">
-        <v>69.60829445301275</v>
+        <v>69.78287595145918</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9089294765052655</v>
+        <v>0.9051745558230836</v>
       </c>
       <c r="E10" t="n">
-        <v>3.575880486199317</v>
+        <v>3.988536341766694</v>
       </c>
       <c r="F10" t="n">
-        <v>8.413363340886978</v>
+        <v>8.413352512361277</v>
       </c>
       <c r="G10" t="n">
-        <v>56.71719933392857</v>
+        <v>56.4828922833604</v>
       </c>
       <c r="H10" t="n">
-        <v>5.508749806533141</v>
+        <v>5.508742716427027</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2329380257886877</v>
+        <v>0.2329377259828553</v>
       </c>
       <c r="J10" t="n">
-        <v>1.001590873915117</v>
+        <v>1.001589584804914</v>
       </c>
       <c r="K10" t="n">
-        <v>23.64134865624293</v>
+        <v>23.46677427947376</v>
       </c>
       <c r="L10" t="n">
-        <v>6.742593079355137</v>
+        <v>6.742585965868738</v>
       </c>
       <c r="M10" t="n">
-        <v>99.9922361886108</v>
+        <v>99.99223619680168</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>73.89570160820493</v>
+        <v>73.93564892229071</v>
       </c>
       <c r="C11" t="n">
-        <v>67.18477540554974</v>
+        <v>67.224731357018</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8679093425052735</v>
+        <v>0.8619243784215055</v>
       </c>
       <c r="E11" t="n">
-        <v>3.751106378886068</v>
+        <v>4.170520592217484</v>
       </c>
       <c r="F11" t="n">
-        <v>8.414100101477231</v>
+        <v>8.414088872950536</v>
       </c>
       <c r="G11" t="n">
-        <v>54.15754297232908</v>
+        <v>53.78408121350192</v>
       </c>
       <c r="H11" t="n">
-        <v>5.509232209300569</v>
+        <v>5.509224857289042</v>
       </c>
       <c r="I11" t="n">
-        <v>0.194132020197513</v>
+        <v>0.1941317611304059</v>
       </c>
       <c r="J11" t="n">
-        <v>1.001678583509194</v>
+        <v>1.001677246779826</v>
       </c>
       <c r="K11" t="n">
-        <v>26.10429839179508</v>
+        <v>26.06435107770927</v>
       </c>
       <c r="L11" t="n">
-        <v>6.70445570193883</v>
+        <v>6.70444707288432</v>
       </c>
       <c r="M11" t="n">
-        <v>99.99352949928365</v>
+        <v>99.9935295076116</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>70.75844827946791</v>
+        <v>70.60602213090657</v>
       </c>
       <c r="C12" t="n">
-        <v>64.08036824704362</v>
+        <v>63.92795101030872</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8160493149872673</v>
+        <v>0.8074186697756655</v>
       </c>
       <c r="E12" t="n">
-        <v>3.932984268098456</v>
+        <v>4.327758679640118</v>
       </c>
       <c r="F12" t="n">
-        <v>8.414741395432722</v>
+        <v>8.414731549738772</v>
       </c>
       <c r="G12" t="n">
-        <v>50.92147725520549</v>
+        <v>50.38292499400151</v>
       </c>
       <c r="H12" t="n">
-        <v>5.509652104152377</v>
+        <v>5.509645657567054</v>
       </c>
       <c r="I12" t="n">
-        <v>0.16178901356389</v>
+        <v>0.161788824262159</v>
       </c>
       <c r="J12" t="n">
-        <v>1.001754928027705</v>
+        <v>1.001753755921282</v>
       </c>
       <c r="K12" t="n">
-        <v>29.2415517205321</v>
+        <v>29.39397786909345</v>
       </c>
       <c r="L12" t="n">
-        <v>6.67268747630769</v>
+        <v>6.672678571677539</v>
       </c>
       <c r="M12" t="n">
-        <v>99.99460744388341</v>
+        <v>99.9946074510797</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>66.55095250842326</v>
+        <v>66.25565261646285</v>
       </c>
       <c r="C13" t="n">
-        <v>59.90022715900761</v>
+        <v>59.6049350487488</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7540360078531114</v>
+        <v>0.7421814984119528</v>
       </c>
       <c r="E13" t="n">
-        <v>3.683079879323678</v>
+        <v>4.139368976848146</v>
       </c>
       <c r="F13" t="n">
-        <v>8.415309675407981</v>
+        <v>8.415302361360574</v>
       </c>
       <c r="G13" t="n">
-        <v>47.05184689003416</v>
+        <v>46.31212550090584</v>
       </c>
       <c r="H13" t="n">
-        <v>5.510024192231415</v>
+        <v>5.510019403271805</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1348332831671949</v>
+        <v>0.1348331659787534</v>
       </c>
       <c r="J13" t="n">
-        <v>1.001822580405712</v>
+        <v>1.001821709685783</v>
       </c>
       <c r="K13" t="n">
-        <v>33.44904749157674</v>
+        <v>33.74434738353713</v>
       </c>
       <c r="L13" t="n">
-        <v>6.646231210149991</v>
+        <v>6.646223433706803</v>
       </c>
       <c r="M13" t="n">
-        <v>99.99550586073434</v>
+        <v>99.99550586599274</v>
       </c>
     </row>
   </sheetData>

--- a/4.1 Myrmidon Happy reef/output/yearly_benthic_cover_growth_param_0.5.xlsx
+++ b/4.1 Myrmidon Happy reef/output/yearly_benthic_cover_growth_param_0.5.xlsx
@@ -541,34 +541,34 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>80.98177313948561</v>
+        <v>80.19925567075651</v>
       </c>
       <c r="C3" t="n">
-        <v>73.6206620283745</v>
+        <v>72.83814455964539</v>
       </c>
       <c r="D3" t="n">
-        <v>1.000343130411954</v>
+        <v>0.9983467583264635</v>
       </c>
       <c r="E3" t="n">
-        <v>1.821286752886324</v>
+        <v>1.165286581233882</v>
       </c>
       <c r="F3" t="n">
-        <v>8.402882295460415</v>
+        <v>8.402910428240389</v>
       </c>
       <c r="G3" t="n">
-        <v>62.42141133770593</v>
+        <v>62.29683771957131</v>
       </c>
       <c r="H3" t="n">
-        <v>5.501887217265748</v>
+        <v>5.50190563753835</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8336192753432952</v>
+        <v>0.8336220662936894</v>
       </c>
       <c r="J3" t="n">
-        <v>1.000343130411954</v>
+        <v>1.000346479552427</v>
       </c>
       <c r="K3" t="n">
-        <v>19.01822686051439</v>
+        <v>19.8007443292435</v>
       </c>
       <c r="L3" t="n">
         <v>7.333333333333333</v>
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>81.25472531960634</v>
+        <v>79.62116679407019</v>
       </c>
       <c r="C4" t="n">
-        <v>74.03465615149415</v>
+        <v>72.40107345322654</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9993796030037663</v>
+        <v>0.9896812987417886</v>
       </c>
       <c r="E4" t="n">
-        <v>2.289816196686135</v>
+        <v>1.270986640602291</v>
       </c>
       <c r="F4" t="n">
-        <v>8.405277643830393</v>
+        <v>8.405354951769382</v>
       </c>
       <c r="G4" t="n">
-        <v>62.36128722743501</v>
+        <v>61.75611304148759</v>
       </c>
       <c r="H4" t="n">
-        <v>5.503455600127043</v>
+        <v>5.503506218420428</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6948807575917985</v>
+        <v>0.6948871487904582</v>
       </c>
       <c r="J4" t="n">
-        <v>1.00062829093219</v>
+        <v>1.00063749425826</v>
       </c>
       <c r="K4" t="n">
-        <v>18.74527468039366</v>
+        <v>20.37883320592979</v>
       </c>
       <c r="L4" t="n">
-        <v>7.196913077130448</v>
+        <v>7.196937172335518</v>
       </c>
       <c r="M4" t="n">
-        <v>99.97684390901826</v>
+        <v>99.97684383149186</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>81.53403254146457</v>
+        <v>79.16196422380473</v>
       </c>
       <c r="C5" t="n">
-        <v>74.43157910914572</v>
+        <v>72.05944546633424</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9959193570186317</v>
+        <v>0.9828218029904293</v>
       </c>
       <c r="E5" t="n">
-        <v>2.900648898181288</v>
+        <v>1.35871305607909</v>
       </c>
       <c r="F5" t="n">
-        <v>8.407267967704492</v>
+        <v>8.407404967456928</v>
       </c>
       <c r="G5" t="n">
-        <v>62.14536787796261</v>
+        <v>61.32808050660277</v>
       </c>
       <c r="H5" t="n">
-        <v>5.504758788377941</v>
+        <v>5.504848490596798</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5792044179690595</v>
+        <v>0.5792138563338383</v>
       </c>
       <c r="J5" t="n">
-        <v>1.000865234250535</v>
+        <v>1.000881543744872</v>
       </c>
       <c r="K5" t="n">
-        <v>18.46596745853545</v>
+        <v>20.83803577619528</v>
       </c>
       <c r="L5" t="n">
-        <v>7.083151189052398</v>
+        <v>7.083216336670736</v>
       </c>
       <c r="M5" t="n">
-        <v>99.98069775673356</v>
+        <v>99.98069757920024</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>81.25243784745543</v>
+        <v>78.06716995468015</v>
       </c>
       <c r="C6" t="n">
-        <v>74.24805446490917</v>
+        <v>71.06267243293989</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9891353195859999</v>
+        <v>0.9661213687099868</v>
       </c>
       <c r="E6" t="n">
-        <v>3.14264712699789</v>
+        <v>1.416088304834127</v>
       </c>
       <c r="F6" t="n">
-        <v>8.408933042931052</v>
+        <v>8.409138050960449</v>
       </c>
       <c r="G6" t="n">
-        <v>61.72204394216639</v>
+        <v>60.28597340750316</v>
       </c>
       <c r="H6" t="n">
-        <v>5.505849016204856</v>
+        <v>5.505983247652674</v>
       </c>
       <c r="I6" t="n">
-        <v>0.482765942077446</v>
+        <v>0.4827777118101743</v>
       </c>
       <c r="J6" t="n">
-        <v>1.001063457491792</v>
+        <v>1.001087863209577</v>
       </c>
       <c r="K6" t="n">
-        <v>18.74756215254456</v>
+        <v>21.93283004531985</v>
       </c>
       <c r="L6" t="n">
-        <v>6.988294370936026</v>
+        <v>6.988408247953203</v>
       </c>
       <c r="M6" t="n">
-        <v>99.98391098838977</v>
+        <v>99.98391072621294</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>80.91722991131741</v>
+        <v>77.00091366617768</v>
       </c>
       <c r="C7" t="n">
-        <v>73.99460232083183</v>
+        <v>70.07811730347888</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9781866061672194</v>
+        <v>0.9498489000076895</v>
       </c>
       <c r="E7" t="n">
-        <v>3.579509560935427</v>
+        <v>1.459301142620197</v>
       </c>
       <c r="F7" t="n">
-        <v>8.410326860681794</v>
+        <v>8.410602842957402</v>
       </c>
       <c r="G7" t="n">
-        <v>61.03884422483449</v>
+        <v>59.27057136047981</v>
       </c>
       <c r="H7" t="n">
-        <v>5.506761634970222</v>
+        <v>5.506942337650679</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4023716355518599</v>
+        <v>0.4023848392526743</v>
       </c>
       <c r="J7" t="n">
-        <v>1.001229388176404</v>
+        <v>1.001262243209214</v>
       </c>
       <c r="K7" t="n">
-        <v>19.08277008868259</v>
+        <v>22.99908633382233</v>
       </c>
       <c r="L7" t="n">
-        <v>6.909217425427853</v>
+        <v>6.909385870704064</v>
       </c>
       <c r="M7" t="n">
-        <v>99.98658983494228</v>
+        <v>99.98658950800527</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>80.05100445942934</v>
+        <v>75.38862477008766</v>
       </c>
       <c r="C8" t="n">
-        <v>73.19652675011304</v>
+        <v>68.53392213320464</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9614605618553075</v>
+        <v>0.9251573094424067</v>
       </c>
       <c r="E8" t="n">
-        <v>3.838647197604469</v>
+        <v>1.47726126745648</v>
       </c>
       <c r="F8" t="n">
-        <v>8.411501302720854</v>
+        <v>8.411850010522883</v>
       </c>
       <c r="G8" t="n">
-        <v>59.99513905977118</v>
+        <v>57.72981610920616</v>
       </c>
       <c r="H8" t="n">
-        <v>5.50753061487675</v>
+        <v>5.507758935461411</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3353565198959083</v>
+        <v>0.3353704224598787</v>
       </c>
       <c r="J8" t="n">
-        <v>1.001369202704864</v>
+        <v>1.001410715538438</v>
       </c>
       <c r="K8" t="n">
-        <v>19.94899554057068</v>
+        <v>24.61137522991234</v>
       </c>
       <c r="L8" t="n">
-        <v>6.843300719439842</v>
+        <v>6.843525280237122</v>
       </c>
       <c r="M8" t="n">
-        <v>99.98882301012355</v>
+        <v>99.9888226433541</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>78.54465005194119</v>
+        <v>73.10975898647882</v>
       </c>
       <c r="C9" t="n">
-        <v>71.74697100889365</v>
+        <v>66.31179813836073</v>
       </c>
       <c r="D9" t="n">
-        <v>0.937787834798256</v>
+        <v>0.8902095252385456</v>
       </c>
       <c r="E9" t="n">
-        <v>3.887233508777706</v>
+        <v>1.468042937377727</v>
       </c>
       <c r="F9" t="n">
-        <v>8.412499031895385</v>
+        <v>8.412922008011115</v>
       </c>
       <c r="G9" t="n">
-        <v>58.51796089141116</v>
+        <v>55.54907437488522</v>
       </c>
       <c r="H9" t="n">
-        <v>5.508183889931503</v>
+        <v>5.508460838578706</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2794969151396284</v>
+        <v>0.2795109681004758</v>
       </c>
       <c r="J9" t="n">
-        <v>1.001487979987546</v>
+        <v>1.001538334287037</v>
       </c>
       <c r="K9" t="n">
-        <v>21.45534994805882</v>
+        <v>26.89024101352118</v>
       </c>
       <c r="L9" t="n">
-        <v>6.788363584161537</v>
+        <v>6.788645003049749</v>
       </c>
       <c r="M9" t="n">
-        <v>99.99068454111401</v>
+        <v>99.99068415493167</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>76.53322572052625</v>
+        <v>70.4852286366776</v>
       </c>
       <c r="C10" t="n">
-        <v>69.78287595145918</v>
+        <v>63.73453946350313</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9051745558230836</v>
+        <v>0.8499562372117361</v>
       </c>
       <c r="E10" t="n">
-        <v>3.988536341766694</v>
+        <v>1.440486556548024</v>
       </c>
       <c r="F10" t="n">
-        <v>8.413352512361277</v>
+        <v>8.413848822779178</v>
       </c>
       <c r="G10" t="n">
-        <v>56.4828922833604</v>
+        <v>53.03726920201231</v>
       </c>
       <c r="H10" t="n">
-        <v>5.508742716427027</v>
+        <v>5.509067681581604</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2329377259828553</v>
+        <v>0.2329514671662845</v>
       </c>
       <c r="J10" t="n">
-        <v>1.001589584804914</v>
+        <v>1.001648669378473</v>
       </c>
       <c r="K10" t="n">
-        <v>23.46677427947376</v>
+        <v>29.5147713633224</v>
       </c>
       <c r="L10" t="n">
-        <v>6.742585965868738</v>
+        <v>6.74292497961614</v>
       </c>
       <c r="M10" t="n">
-        <v>99.99223619680168</v>
+        <v>99.99223580644166</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>73.93564892229071</v>
+        <v>67.52063584850308</v>
       </c>
       <c r="C11" t="n">
-        <v>67.224731357018</v>
+        <v>60.80932240081648</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8619243784215055</v>
+        <v>0.8044906225642147</v>
       </c>
       <c r="E11" t="n">
-        <v>4.170520592217484</v>
+        <v>1.395789935291871</v>
       </c>
       <c r="F11" t="n">
-        <v>8.414088872950536</v>
+        <v>8.414655245495771</v>
       </c>
       <c r="G11" t="n">
-        <v>53.78408121350192</v>
+        <v>50.20021484800698</v>
       </c>
       <c r="H11" t="n">
-        <v>5.509224857289042</v>
+        <v>5.509595696455564</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1941317611304059</v>
+        <v>0.1941448286058417</v>
       </c>
       <c r="J11" t="n">
-        <v>1.001677246779826</v>
+        <v>1.00174467208283</v>
       </c>
       <c r="K11" t="n">
-        <v>26.06435107770927</v>
+        <v>32.47936415149693</v>
       </c>
       <c r="L11" t="n">
-        <v>6.70444707288432</v>
+        <v>6.704842573598649</v>
       </c>
       <c r="M11" t="n">
-        <v>99.9935295076116</v>
+        <v>99.99352912591206</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>70.60602213090657</v>
+        <v>64.09151587101329</v>
       </c>
       <c r="C12" t="n">
-        <v>63.92795101030872</v>
+        <v>57.41299523339763</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8074186697756655</v>
+        <v>0.7503329022158252</v>
       </c>
       <c r="E12" t="n">
-        <v>4.327758679640118</v>
+        <v>1.431357247164664</v>
       </c>
       <c r="F12" t="n">
-        <v>8.414731549738772</v>
+        <v>8.415363347224517</v>
       </c>
       <c r="G12" t="n">
-        <v>50.38292499400151</v>
+        <v>46.82077309826748</v>
       </c>
       <c r="H12" t="n">
-        <v>5.509645657567054</v>
+        <v>5.510059334492243</v>
       </c>
       <c r="I12" t="n">
-        <v>0.161788824262159</v>
+        <v>0.1618009717408736</v>
       </c>
       <c r="J12" t="n">
-        <v>1.001753755921282</v>
+        <v>1.00182896990768</v>
       </c>
       <c r="K12" t="n">
-        <v>29.39397786909345</v>
+        <v>35.90848412898673</v>
       </c>
       <c r="L12" t="n">
-        <v>6.672678571677539</v>
+        <v>6.673127725709929</v>
       </c>
       <c r="M12" t="n">
-        <v>99.9946074510797</v>
+        <v>99.99460708809428</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>66.25565261646285</v>
+        <v>59.71441343216921</v>
       </c>
       <c r="C13" t="n">
-        <v>59.6049350487488</v>
+        <v>53.06319651321466</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7421814984119528</v>
+        <v>0.6833615018412281</v>
       </c>
       <c r="E13" t="n">
-        <v>4.139368976848146</v>
+        <v>1.326074670797897</v>
       </c>
       <c r="F13" t="n">
-        <v>8.415302361360574</v>
+        <v>8.415996786540067</v>
       </c>
       <c r="G13" t="n">
-        <v>46.31212550090584</v>
+        <v>42.64175771489263</v>
       </c>
       <c r="H13" t="n">
-        <v>5.510019403271805</v>
+        <v>5.510474086425043</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1348331659787534</v>
+        <v>0.1348442923223434</v>
       </c>
       <c r="J13" t="n">
-        <v>1.001821709685783</v>
+        <v>1.001904379350008</v>
       </c>
       <c r="K13" t="n">
-        <v>33.74434738353713</v>
+        <v>40.28558656783078</v>
       </c>
       <c r="L13" t="n">
-        <v>6.646223433706803</v>
+        <v>6.646722447517318</v>
       </c>
       <c r="M13" t="n">
-        <v>99.99550586599274</v>
+        <v>99.99550552856277</v>
       </c>
     </row>
   </sheetData>

--- a/4.1 Myrmidon Happy reef/output/yearly_benthic_cover_growth_param_0.5.xlsx
+++ b/4.1 Myrmidon Happy reef/output/yearly_benthic_cover_growth_param_0.5.xlsx
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>80.19925567075651</v>
+        <v>80.30010052465241</v>
       </c>
       <c r="C3" t="n">
-        <v>72.83814455964539</v>
+        <v>72.93898941354129</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9983467583264635</v>
+        <v>0.9992326295162328</v>
       </c>
       <c r="E3" t="n">
-        <v>1.165286581233882</v>
+        <v>1.209974050053386</v>
       </c>
       <c r="F3" t="n">
-        <v>8.402910428240389</v>
+        <v>8.40290677191526</v>
       </c>
       <c r="G3" t="n">
-        <v>62.29683771957131</v>
+        <v>62.35211608181293</v>
       </c>
       <c r="H3" t="n">
-        <v>5.50190563753835</v>
+        <v>5.501903243515944</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8336220662936894</v>
+        <v>0.8336217035630219</v>
       </c>
       <c r="J3" t="n">
-        <v>1.000346479552427</v>
+        <v>1.000346044275626</v>
       </c>
       <c r="K3" t="n">
-        <v>19.8007443292435</v>
+        <v>19.6998994753476</v>
       </c>
       <c r="L3" t="n">
         <v>7.333333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>99.97222222222221</v>
+        <v>99.97222222222223</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79.62116679407019</v>
+        <v>79.83497076948477</v>
       </c>
       <c r="C4" t="n">
-        <v>72.40107345322654</v>
+        <v>72.61488057029173</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9896812987417886</v>
+        <v>0.9923215167207088</v>
       </c>
       <c r="E4" t="n">
-        <v>1.270986640602291</v>
+        <v>1.317419745189021</v>
       </c>
       <c r="F4" t="n">
-        <v>8.405354951769382</v>
+        <v>8.4053447448075</v>
       </c>
       <c r="G4" t="n">
-        <v>61.75611304148759</v>
+        <v>61.92086264337223</v>
       </c>
       <c r="H4" t="n">
-        <v>5.503506218420428</v>
+        <v>5.503499535290625</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6948871487904582</v>
+        <v>0.6948863049609375</v>
       </c>
       <c r="J4" t="n">
-        <v>1.00063749425826</v>
+        <v>1.00063627914375</v>
       </c>
       <c r="K4" t="n">
-        <v>20.37883320592979</v>
+        <v>20.16502923051521</v>
       </c>
       <c r="L4" t="n">
-        <v>7.196937172335518</v>
+        <v>7.196934040760754</v>
       </c>
       <c r="M4" t="n">
-        <v>99.97684383149186</v>
+        <v>99.9768438415677</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>79.16196422380473</v>
+        <v>79.47110467314313</v>
       </c>
       <c r="C5" t="n">
-        <v>72.05944546633424</v>
+        <v>72.36859454054793</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9828218029904293</v>
+        <v>0.9869397331523279</v>
       </c>
       <c r="E5" t="n">
-        <v>1.35871305607909</v>
+        <v>1.406810248904471</v>
       </c>
       <c r="F5" t="n">
-        <v>8.407404967456928</v>
+        <v>8.407386779091999</v>
       </c>
       <c r="G5" t="n">
-        <v>61.32808050660277</v>
+        <v>61.58503934870527</v>
       </c>
       <c r="H5" t="n">
-        <v>5.504848490596798</v>
+        <v>5.504836581548332</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5792138563338383</v>
+        <v>0.5792126032773919</v>
       </c>
       <c r="J5" t="n">
-        <v>1.000881543744872</v>
+        <v>1.000879378463333</v>
       </c>
       <c r="K5" t="n">
-        <v>20.83803577619528</v>
+        <v>20.52889532685688</v>
       </c>
       <c r="L5" t="n">
-        <v>7.083216336670736</v>
+        <v>7.083207735235156</v>
       </c>
       <c r="M5" t="n">
-        <v>99.98069757920024</v>
+        <v>99.98069760263996</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>78.06716995468015</v>
+        <v>78.47514620309954</v>
       </c>
       <c r="C6" t="n">
-        <v>71.06267243293989</v>
+        <v>71.47066383471014</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9661213687099868</v>
+        <v>0.9717752688397053</v>
       </c>
       <c r="E6" t="n">
-        <v>1.416088304834127</v>
+        <v>1.465657108183546</v>
       </c>
       <c r="F6" t="n">
-        <v>8.409138050960449</v>
+        <v>8.40911084334053</v>
       </c>
       <c r="G6" t="n">
-        <v>60.28597340750316</v>
+        <v>60.63877677559763</v>
       </c>
       <c r="H6" t="n">
-        <v>5.505983247652674</v>
+        <v>5.505965433139633</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4827777118101743</v>
+        <v>0.4827761497912837</v>
       </c>
       <c r="J6" t="n">
-        <v>1.001087863209577</v>
+        <v>1.001084624207206</v>
       </c>
       <c r="K6" t="n">
-        <v>21.93283004531985</v>
+        <v>21.52485379690046</v>
       </c>
       <c r="L6" t="n">
-        <v>6.988408247953203</v>
+        <v>6.988393129409491</v>
       </c>
       <c r="M6" t="n">
-        <v>99.98391072621294</v>
+        <v>99.98391076102008</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>77.00091366617768</v>
+        <v>77.48542849088292</v>
       </c>
       <c r="C7" t="n">
-        <v>70.07811730347888</v>
+        <v>70.56265452677137</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9498489000076895</v>
+        <v>0.9566928892852081</v>
       </c>
       <c r="E7" t="n">
-        <v>1.459301142620197</v>
+        <v>1.509973315081998</v>
       </c>
       <c r="F7" t="n">
-        <v>8.410602842957402</v>
+        <v>8.410566465016984</v>
       </c>
       <c r="G7" t="n">
-        <v>59.27057136047981</v>
+        <v>59.697636291397</v>
       </c>
       <c r="H7" t="n">
-        <v>5.506942337650679</v>
+        <v>5.506918518761121</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4023848392526743</v>
+        <v>0.4023830988385826</v>
       </c>
       <c r="J7" t="n">
-        <v>1.001262243209214</v>
+        <v>1.001257912502022</v>
       </c>
       <c r="K7" t="n">
-        <v>22.99908633382233</v>
+        <v>22.51457150911707</v>
       </c>
       <c r="L7" t="n">
-        <v>6.909385870704064</v>
+        <v>6.909363515506243</v>
       </c>
       <c r="M7" t="n">
-        <v>99.98658950800527</v>
+        <v>99.98658955139469</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>75.38862477008766</v>
+        <v>75.96260910235591</v>
       </c>
       <c r="C8" t="n">
-        <v>68.53392213320464</v>
+        <v>69.10793611375954</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9251573094424067</v>
+        <v>0.9333944258783912</v>
       </c>
       <c r="E8" t="n">
-        <v>1.47726126745648</v>
+        <v>1.529095509200454</v>
       </c>
       <c r="F8" t="n">
-        <v>8.411850010522883</v>
+        <v>8.41180419671138</v>
       </c>
       <c r="G8" t="n">
-        <v>57.72981610920616</v>
+        <v>58.24381217481162</v>
       </c>
       <c r="H8" t="n">
-        <v>5.507758935461411</v>
+        <v>5.507728938322928</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3353704224598787</v>
+        <v>0.3353685959178815</v>
       </c>
       <c r="J8" t="n">
-        <v>1.001410715538438</v>
+        <v>1.00140526151326</v>
       </c>
       <c r="K8" t="n">
-        <v>24.61137522991234</v>
+        <v>24.03739089764409</v>
       </c>
       <c r="L8" t="n">
-        <v>6.843525280237122</v>
+        <v>6.843495680295296</v>
       </c>
       <c r="M8" t="n">
-        <v>99.9888226433541</v>
+        <v>99.98882269169891</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>73.10975898647882</v>
+        <v>73.79803595807998</v>
       </c>
       <c r="C9" t="n">
-        <v>66.31179813836073</v>
+        <v>67.00011213398119</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8902095252385456</v>
+        <v>0.9002265035689457</v>
       </c>
       <c r="E9" t="n">
-        <v>1.468042937377727</v>
+        <v>1.521344359793531</v>
       </c>
       <c r="F9" t="n">
-        <v>8.412922008011115</v>
+        <v>8.412866183390044</v>
       </c>
       <c r="G9" t="n">
-        <v>55.54907437488522</v>
+        <v>56.17413382270222</v>
       </c>
       <c r="H9" t="n">
-        <v>5.508460838578706</v>
+        <v>5.508424286743482</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2795109681004758</v>
+        <v>0.2795091133829514</v>
       </c>
       <c r="J9" t="n">
-        <v>1.001538334287037</v>
+        <v>1.001531688498815</v>
       </c>
       <c r="K9" t="n">
-        <v>26.89024101352118</v>
+        <v>26.20196404192001</v>
       </c>
       <c r="L9" t="n">
-        <v>6.788645003049749</v>
+        <v>6.788608029767756</v>
       </c>
       <c r="M9" t="n">
-        <v>99.99068415493167</v>
+        <v>99.99068420566896</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70.4852286366776</v>
+        <v>71.27209944898188</v>
       </c>
       <c r="C10" t="n">
-        <v>63.73453946350313</v>
+        <v>64.52145507054868</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8499562372117361</v>
+        <v>0.8615134993447229</v>
       </c>
       <c r="E10" t="n">
-        <v>1.440486556548024</v>
+        <v>1.494745974987199</v>
       </c>
       <c r="F10" t="n">
-        <v>8.413848822779178</v>
+        <v>8.413782752494587</v>
       </c>
       <c r="G10" t="n">
-        <v>53.03726920201231</v>
+        <v>53.75844235911071</v>
       </c>
       <c r="H10" t="n">
-        <v>5.509067681581604</v>
+        <v>5.509024421276218</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2329514671662845</v>
+        <v>0.2329496379000289</v>
       </c>
       <c r="J10" t="n">
-        <v>1.001648669378473</v>
+        <v>1.001640803868403</v>
       </c>
       <c r="K10" t="n">
-        <v>29.5147713633224</v>
+        <v>28.72790055101813</v>
       </c>
       <c r="L10" t="n">
-        <v>6.74292497961614</v>
+        <v>6.742880236394757</v>
       </c>
       <c r="M10" t="n">
-        <v>99.99223580644166</v>
+        <v>99.99223585796157</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>67.52063584850308</v>
+        <v>68.38116883051323</v>
       </c>
       <c r="C11" t="n">
-        <v>60.80932240081648</v>
+        <v>61.66990808384357</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8044906225642147</v>
+        <v>0.81718211342363</v>
       </c>
       <c r="E11" t="n">
-        <v>1.395789935291871</v>
+        <v>1.451819376815676</v>
       </c>
       <c r="F11" t="n">
-        <v>8.414655245495771</v>
+        <v>8.414579013433976</v>
       </c>
       <c r="G11" t="n">
-        <v>50.20021484800698</v>
+        <v>50.99216387763451</v>
       </c>
       <c r="H11" t="n">
-        <v>5.509595696455564</v>
+        <v>5.50954578260558</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1941448286058417</v>
+        <v>0.1941430697624739</v>
       </c>
       <c r="J11" t="n">
-        <v>1.00174467208283</v>
+        <v>1.001735596837378</v>
       </c>
       <c r="K11" t="n">
-        <v>32.47936415149693</v>
+        <v>31.61883116948679</v>
       </c>
       <c r="L11" t="n">
-        <v>6.704842573598649</v>
+        <v>6.704789923394646</v>
       </c>
       <c r="M11" t="n">
-        <v>99.99352912591206</v>
+        <v>99.99352917672499</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>64.09151587101329</v>
+        <v>64.9637679086776</v>
       </c>
       <c r="C12" t="n">
-        <v>57.41299523339763</v>
+        <v>58.28530777471695</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7503329022158252</v>
+        <v>0.763326245429151</v>
       </c>
       <c r="E12" t="n">
-        <v>1.431357247164664</v>
+        <v>1.479985083373623</v>
       </c>
       <c r="F12" t="n">
-        <v>8.415363347224517</v>
+        <v>8.415277594212855</v>
       </c>
       <c r="G12" t="n">
-        <v>46.82077309826748</v>
+        <v>47.63155771477901</v>
       </c>
       <c r="H12" t="n">
-        <v>5.510059334492243</v>
+        <v>5.510003186686989</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1618009717408736</v>
+        <v>0.1617993229801435</v>
       </c>
       <c r="J12" t="n">
-        <v>1.00182896990768</v>
+        <v>1.001818761215816</v>
       </c>
       <c r="K12" t="n">
-        <v>35.90848412898673</v>
+        <v>35.03623209132242</v>
       </c>
       <c r="L12" t="n">
-        <v>6.673127725709929</v>
+        <v>6.673067270911687</v>
       </c>
       <c r="M12" t="n">
-        <v>99.99460708809428</v>
+        <v>99.99460713695105</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>59.71441343216921</v>
+        <v>60.60331832915239</v>
       </c>
       <c r="C13" t="n">
-        <v>53.06319651321466</v>
+        <v>53.95216918646113</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6833615018412281</v>
+        <v>0.6966419826337984</v>
       </c>
       <c r="E13" t="n">
-        <v>1.326074670797897</v>
+        <v>1.373167222392978</v>
       </c>
       <c r="F13" t="n">
-        <v>8.415996786540067</v>
+        <v>8.415901729087706</v>
       </c>
       <c r="G13" t="n">
-        <v>42.64175771489263</v>
+        <v>43.47045971634901</v>
       </c>
       <c r="H13" t="n">
-        <v>5.510474086425043</v>
+        <v>5.510411846426474</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1348442923223434</v>
+        <v>0.1348427692757907</v>
       </c>
       <c r="J13" t="n">
-        <v>1.001904379350008</v>
+        <v>1.001893062986632</v>
       </c>
       <c r="K13" t="n">
-        <v>40.28558656783078</v>
+        <v>39.39668167084761</v>
       </c>
       <c r="L13" t="n">
-        <v>6.646722447517318</v>
+        <v>6.646654717052925</v>
       </c>
       <c r="M13" t="n">
-        <v>99.99550552856277</v>
+        <v>99.99550557436167</v>
       </c>
     </row>
   </sheetData>
